--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M09/run_2/CF_M09_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M09/run_2/CF_M09_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.75</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.7347</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.7907</v>
       </c>
       <c r="D3" t="n">
+        <v>0.8095</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9736</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.4</v>
       </c>
       <c r="D4" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8429</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7907</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_10', 'AU_11']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_39</t>
@@ -1233,7 +1245,6 @@
           <t>business service, functional service</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M09_AU06, CF_M09_AU19</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M09_AU20</t>
@@ -1308,13 +1318,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Business layer</t>
@@ -1338,13 +1346,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M09_AU09</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1390,13 +1396,11 @@
           <t>['AU_35']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>REST</t>
@@ -1420,13 +1424,11 @@
           <t>CF_M09_AU20</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M09_AU22</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1472,13 +1474,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>RDS</t>
@@ -1502,13 +1502,11 @@
           <t>CF_M09_AU39</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M09_AU23</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1554,13 +1552,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -1579,14 +1575,11 @@
       <c r="P6" t="n">
         <v>55</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1607,7 +1600,6 @@
       <c r="D7" t="n">
         <v>0.8951</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1628,7 +1620,6 @@
           <t>['AU_08', 'AU_09']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_38</t>
@@ -1639,7 +1630,6 @@
           <t>dispatcher, store</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1658,7 +1648,6 @@
           <t>CF_M09_AU13, CF_M09_AU14</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M09_AU16</t>
@@ -1709,14 +1698,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Client-Server Architecture</t>
@@ -1735,14 +1721,11 @@
       <c r="P8" t="n">
         <v>55</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M09_P01</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1788,13 +1771,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Business layer (Backend)</t>
@@ -1818,13 +1799,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M09_AU19</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1870,13 +1849,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -1900,13 +1877,11 @@
           <t>CF_M09_AU39</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M09_AU25</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1952,13 +1927,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Presentation layer</t>
@@ -1982,13 +1955,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M09_AU08</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2034,13 +2005,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Data layer</t>
@@ -2064,13 +2033,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M09_AU10</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2116,13 +2083,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>P_07</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Hook pattern</t>
@@ -2146,13 +2111,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M09_P07</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2193,14 +2156,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_26</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Typescript</t>
@@ -2224,13 +2184,11 @@
           <t>CF_M09_AU26</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M09_AU28</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2276,13 +2234,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Provider pattern</t>
@@ -2306,13 +2262,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M09_P05</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2358,13 +2312,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Observer pattern</t>
@@ -2388,13 +2340,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M09_P04</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2440,13 +2390,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>React</t>
@@ -2470,13 +2418,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2522,13 +2468,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_28</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Material UI</t>
@@ -2552,13 +2496,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M09_AU30</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2599,14 +2541,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Player</t>
@@ -2625,14 +2564,11 @@
       <c r="P19" t="n">
         <v>9</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M09_AU04</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2678,13 +2614,11 @@
           <t>['AU_12', 'AU_41']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -2708,13 +2642,11 @@
           <t>CF_M09_AU23</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M09_AU24</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2760,13 +2692,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Dispatcher</t>
@@ -2790,13 +2720,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M09_AU13</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2842,13 +2770,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>View</t>
@@ -2872,13 +2798,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M09_AU11</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2924,13 +2848,11 @@
           <t>['AU_35']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2949,14 +2871,11 @@
       <c r="P23" t="n">
         <v>55</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M09_AU40</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2997,14 +2916,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_31</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Shadcn</t>
@@ -3028,13 +2944,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M09_AU32</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3080,13 +2994,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Actions</t>
@@ -3110,13 +3022,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M09_AU12</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3162,13 +3072,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Store</t>
@@ -3192,13 +3100,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M09_AU14</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3244,13 +3150,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_25</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -3274,13 +3178,11 @@
           <t>CF_M09_AU33</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M09_AU02</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3321,14 +3223,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>AU_27</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>TypeORM</t>
@@ -3352,13 +3251,11 @@
           <t>CF_M09_AU33</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CF_M09_AU29</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3404,13 +3301,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Client</t>
@@ -3434,13 +3329,11 @@
           <t>CF_M09_P01</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M09_AU06</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3486,13 +3379,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Redux</t>
@@ -3516,13 +3407,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CF_M09_AU17</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3563,14 +3452,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>AU_30</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>NextJS</t>
@@ -3594,13 +3480,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>CF_M09_AU31</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3646,13 +3530,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Flux</t>
@@ -3676,13 +3558,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3723,14 +3603,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>P_06</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>Module Pattern</t>
@@ -3749,14 +3626,11 @@
       <c r="P33" t="n">
         <v>59</v>
       </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>CF_M09_P06</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3797,14 +3671,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>AU_29</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>AWS</t>
@@ -3823,14 +3694,11 @@
       <c r="P34" t="n">
         <v>9</v>
       </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>CF_M09_AU03</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3876,13 +3744,11 @@
           <t>['AU_14', 'AU_43']</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -3906,13 +3772,11 @@
           <t>CF_M09_AU10</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>CF_M09_AU27</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3958,13 +3822,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>User Cache</t>
@@ -3988,13 +3850,11 @@
           <t>CF_M09_AU39</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>CF_M09_AU26</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4040,13 +3900,11 @@
           <t>['AU_39']</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>TCP</t>
@@ -4070,13 +3928,11 @@
           <t>CF_M09_AU20</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>CF_M09_AU21</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4150,7 +4006,6 @@
           <t>Server</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Por un lado está el cliente, quien realiza las diferentes peticiones, y por otro lado está el servidor, quien las recibe y las procesa.</t>
@@ -4186,7 +4041,6 @@
           <t>Functional Service</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Servicio functional: Este es el servicio que realiza toda la lógica importante de la plataforma.</t>
@@ -4222,7 +4076,6 @@
           <t>Screen</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Las pantallas profesionales o pantallas SOC tienen un player integrado en su interior.</t>
@@ -4258,7 +4111,6 @@
           <t>Network Switch</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Como ejemplo, un activo puede ser la propia pantalla, un commutator de red, un player, etc.</t>
@@ -4294,7 +4146,6 @@
           <t>Figma</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Todos los prototipos se han creado utilizando la herramienta Figma</t>
@@ -4330,7 +4181,6 @@
           <t>Swagger</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Los decoradores @ApiResponse son parte de Swagger y permiten generar documentación de la API.</t>
@@ -4366,7 +4216,6 @@
           <t>SMPLRSpace</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>El primer paso para visualizar el mapa 3D es crear este mapa en la página web que ofrece la librería utilizada (SMPLRSpace).</t>
@@ -4397,7 +4246,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>client, server</t>
@@ -4433,7 +4281,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>presentation layer, view</t>
@@ -4469,7 +4316,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>business layer, server</t>
@@ -4505,7 +4351,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>functional service, data layer</t>
@@ -4541,7 +4386,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>functional service, rds database</t>
@@ -4577,7 +4421,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>functional service, amazon s3 storage</t>
@@ -4613,7 +4456,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>business service, user cache</t>
@@ -4710,7 +4552,6 @@
           <t>Waapiti Platform</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The main objective of this work is the development of an asset management module that expands the Waapiti software platform and allows us to solve a series of problems and needs of the company.</t>
@@ -4721,7 +4562,6 @@
           <t>AU_41</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0.67</v>
       </c>
@@ -4737,7 +4577,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>client, waapiti platform</t>
@@ -4773,7 +4612,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>actions, store</t>
@@ -4814,7 +4652,6 @@
           <t>Presentation layer (Backend)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
@@ -4850,7 +4687,6 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
@@ -4886,7 +4722,6 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
@@ -4922,7 +4757,6 @@
           <t>Modules</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Modules are classes that allow NestJS to organize the application.</t>
@@ -4958,7 +4792,6 @@
           <t>Controllers</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Controllers are responsible for receiving and processing HTTP requests.</t>
@@ -4994,7 +4827,6 @@
           <t>Providers</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
@@ -5025,7 +4857,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>client, business layer (backend)</t>
@@ -5041,7 +4872,6 @@
           <t>AU_39</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>0.7227</v>
       </c>
@@ -5062,7 +4892,6 @@
           <t>Data Layer (Backend)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
@@ -5098,7 +4927,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>TypeORM is an ORM (Object Relational Mapping) that allows you to define database entities as TypeScript classes.</t>
